--- a/PPG/Produção.xlsx
+++ b/PPG/Produção.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D9C548-70C1-554A-A816-EB442377D4CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A580F8-3B85-1441-B1DC-FB969E9E8A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="900" yWindow="680" windowWidth="29340" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1551" uniqueCount="1518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="1525">
   <si>
     <t>Aceito</t>
   </si>
@@ -4575,9 +4575,6 @@
     <t>Lócus de controle da saúde e sua associação com cinesiofobia, incapacidade e prognóstico na dor lombar crônica</t>
   </si>
   <si>
-    <t>Segurança do exercício físico em pacientes com insuficiência cardíaca submetidos à infusão de inotrópicos - um estudo de coorte retrospectivo</t>
-  </si>
-  <si>
     <t xml:space="preserve">10.12865/CHSJ.51.04.10 </t>
   </si>
   <si>
@@ -4600,6 +4597,30 @@
   </si>
   <si>
     <t>INCIDÊNCIA E PREVALÊNCIA DE DOR EM PACIENTES VENTILADOS MECANICAMENTE: RESULTADOS PRELIMINARES DE UMA COORTE MULTICÊNTRICA</t>
+  </si>
+  <si>
+    <t>10.1016/j.msksp.2026.103519</t>
+  </si>
+  <si>
+    <t>Responsiveness of central sensitization-related measures in older people with chronic low back pain</t>
+  </si>
+  <si>
+    <t>10.1177/0885066626142219</t>
+  </si>
+  <si>
+    <t>Predicting Extubation Outcomes in Pneumonia – A Systematic Review of Ventilatory Indices</t>
+  </si>
+  <si>
+    <t>Understanding double triggering in patient–ventilator asynchrony: beyond first‑breath classification</t>
+  </si>
+  <si>
+    <t>10.1007/s00134-026-08352-2</t>
+  </si>
+  <si>
+    <t>Safety of physical exercise in heart failure patients undergoing inotropic infusion</t>
+  </si>
+  <si>
+    <t>10.25248/REAS.e23124.2026</t>
   </si>
 </sst>
 </file>
@@ -4763,7 +4784,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="15">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -4833,6 +4854,37 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5100,7 +5152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I652"/>
+  <dimension ref="A1:I654"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.140625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="15" bestFit="1" customWidth="1"/>
@@ -11521,10 +11573,10 @@
         <v>2025</v>
       </c>
       <c r="B585" s="3" t="s">
+        <v>1509</v>
+      </c>
+      <c r="C585" s="3" t="s">
         <v>1510</v>
-      </c>
-      <c r="C585" s="3" t="s">
-        <v>1511</v>
       </c>
     </row>
     <row r="586" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -12137,10 +12189,10 @@
         <v>2026</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>1409</v>
+        <v>1517</v>
       </c>
       <c r="C641" s="3" t="s">
-        <v>1410</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.2">
@@ -12148,26 +12200,32 @@
         <v>2026</v>
       </c>
       <c r="B642" s="3" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C642" s="3" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="643" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A643" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B643" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C643" s="3" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="644" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A644" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B644" s="3" t="s">
         <v>1489</v>
       </c>
-      <c r="C642" s="3" t="s">
+      <c r="C644" s="3" t="s">
         <v>1426</v>
-      </c>
-    </row>
-    <row r="643" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A643" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C643" s="3" t="s">
-        <v>1488</v>
-      </c>
-    </row>
-    <row r="644" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A644" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C644" s="3" t="s">
-        <v>1484</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.2">
@@ -12175,37 +12233,34 @@
         <v>0</v>
       </c>
       <c r="C645" s="3" t="s">
-        <v>1237</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A646" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B646" s="3" t="s">
-        <v>1372</v>
-      </c>
       <c r="C646" s="3" t="s">
-        <v>1492</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A647" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B647" s="3" t="s">
-        <v>1411</v>
-      </c>
       <c r="C647" s="3" t="s">
-        <v>1412</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A648" s="15" t="s">
         <v>0</v>
       </c>
+      <c r="B648" s="3" t="s">
+        <v>1372</v>
+      </c>
       <c r="C648" s="3" t="s">
-        <v>1508</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.2">
@@ -12213,10 +12268,10 @@
         <v>0</v>
       </c>
       <c r="B649" s="3" t="s">
-        <v>1363</v>
+        <v>1411</v>
       </c>
       <c r="C649" s="3" t="s">
-        <v>1362</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.2">
@@ -12224,15 +12279,18 @@
         <v>0</v>
       </c>
       <c r="C650" s="3" t="s">
-        <v>1408</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C651" s="19" t="s">
-        <v>1421</v>
+      <c r="B651" s="3" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C651" s="3" t="s">
+        <v>1362</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.2">
@@ -12240,19 +12298,38 @@
         <v>0</v>
       </c>
       <c r="C652" s="3" t="s">
-        <v>1509</v>
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A653" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B653" s="3" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C653" s="3" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A654" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C654" s="19" t="s">
+        <v>1421</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C652">
-    <sortCondition ref="A2:A652"/>
-    <sortCondition ref="C2:C652"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C654">
+    <sortCondition ref="A2:A654"/>
+    <sortCondition ref="C2:C654"/>
   </sortState>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="containsText" dxfId="11" priority="10" operator="containsText" text="Submetido">
+    <cfRule type="containsText" dxfId="14" priority="10" operator="containsText" text="Submetido">
       <formula>NOT(ISERROR(SEARCH(("Submetido"),(A1))))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="11" operator="containsText" text="Aceito">
+    <cfRule type="containsText" dxfId="13" priority="11" operator="containsText" text="Aceito">
       <formula>NOT(ISERROR(SEARCH(("Aceito"),(A1))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="102">
@@ -12265,10 +12342,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B633:B1048576 B1:B630 C631">
-    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C633:C1048576 C1:C630">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="B449" r:id="rId1" xr:uid="{9BCE4324-8A77-884E-80ED-4C3988C2A1D3}"/>
@@ -12281,7 +12358,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.140625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="3" bestFit="1" customWidth="1"/>
@@ -12710,7 +12787,7 @@
         <v>0</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>1506</v>
@@ -12721,10 +12798,21 @@
         <v>2026</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>1513</v>
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>1521</v>
       </c>
     </row>
   </sheetData>
@@ -12732,11 +12820,8 @@
     <sortCondition ref="A2:A35"/>
     <sortCondition ref="C2:C35"/>
   </sortState>
-  <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="containsText" dxfId="7" priority="10" operator="containsText" text="Aceito">
-      <formula>NOT(ISERROR(SEARCH(("Aceito"),(A1))))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="11">
+  <conditionalFormatting sqref="A1:A40 A42:A1048576">
+    <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -12745,10 +12830,34 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="Aceito">
+      <formula>NOT(ISERROR(SEARCH(("Aceito"),(A1))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A41">
+    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="Submetido">
+      <formula>NOT(ISERROR(SEARCH(("Submetido"),(A41))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF366092"/>
+        <color rgb="FFB8CCE4"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B40 B42:B1048576">
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B41">
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C41">
     <cfRule type="duplicateValues" dxfId="5" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
@@ -14456,7 +14565,7 @@
         <v>2025</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
@@ -14464,7 +14573,7 @@
         <v>2025</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
@@ -14472,7 +14581,7 @@
         <v>2025</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
     </row>
   </sheetData>

--- a/PPG/Produção.xlsx
+++ b/PPG/Produção.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A580F8-3B85-1441-B1DC-FB969E9E8A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33FB30F-C211-CD4D-8F85-1706A159F7C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="900" yWindow="680" windowWidth="29340" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="1525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="1529">
   <si>
     <t>Aceito</t>
   </si>
@@ -4621,6 +4621,18 @@
   </si>
   <si>
     <t>10.25248/REAS.e23124.2026</t>
+  </si>
+  <si>
+    <t>Translation, cross-cultural adaptation, and measurement properties of the Back pain Knowledge and beliefs Survey (BacKS) for the Brazilian population</t>
+  </si>
+  <si>
+    <t>Development and Validation of the Respiratory Secretion Scale (RESES) in Mechanically Ventilated Patients</t>
+  </si>
+  <si>
+    <t>Keeping the abdomen relaxed versus contracted during Pilates improves disability slightly and may improve other outcomes in chronic non-specific low back pain: a randomised trial</t>
+  </si>
+  <si>
+    <t>Persistence of structural reasoning in Brazilian physiotherapy: a cross-sectional study on 'text neck' beliefs</t>
   </si>
 </sst>
 </file>
@@ -5152,7 +5164,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I654"/>
+  <dimension ref="A1:I658"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.140625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="15" bestFit="1" customWidth="1"/>
@@ -12318,6 +12330,38 @@
       </c>
       <c r="C654" s="19" t="s">
         <v>1421</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A655" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C655" s="3" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A656" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C656" s="3" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A657" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C657" s="3" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A658" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C658" s="3" t="s">
+        <v>1528</v>
       </c>
     </row>
   </sheetData>

--- a/PPG/Produção.xlsx
+++ b/PPG/Produção.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33FB30F-C211-CD4D-8F85-1706A159F7C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBDE499E-1B5F-BB45-9E41-8F711F5A953C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="900" yWindow="680" windowWidth="29340" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="1529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="1532">
   <si>
     <t>Aceito</t>
   </si>
@@ -4633,6 +4633,15 @@
   </si>
   <si>
     <t>Persistence of structural reasoning in Brazilian physiotherapy: a cross-sectional study on 'text neck' beliefs</t>
+  </si>
+  <si>
+    <t>10.1007/s10484-026-09779-5</t>
+  </si>
+  <si>
+    <t>The Relationship Between Psychological Factors and Postural Performance under Different Biofeedback Conditions</t>
+  </si>
+  <si>
+    <t>Associação entre o lócus de controle da dor e o risco de quedas em idosos com dor crônica: um estudo transversal de base comunitária</t>
   </si>
 </sst>
 </file>
@@ -5164,7 +5173,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I658"/>
+  <dimension ref="A1:I660"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.140625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="15" bestFit="1" customWidth="1"/>
@@ -12234,18 +12243,21 @@
         <v>2026</v>
       </c>
       <c r="B644" s="3" t="s">
+        <v>1529</v>
+      </c>
+      <c r="C644" s="3" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="645" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A645" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B645" s="3" t="s">
         <v>1489</v>
       </c>
-      <c r="C644" s="3" t="s">
+      <c r="C645" s="3" t="s">
         <v>1426</v>
-      </c>
-    </row>
-    <row r="645" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A645" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C645" s="3" t="s">
-        <v>1488</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.2">
@@ -12253,7 +12265,7 @@
         <v>0</v>
       </c>
       <c r="C646" s="3" t="s">
-        <v>1484</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.2">
@@ -12261,18 +12273,15 @@
         <v>0</v>
       </c>
       <c r="C647" s="3" t="s">
-        <v>1237</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A648" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B648" s="3" t="s">
-        <v>1372</v>
-      </c>
       <c r="C648" s="3" t="s">
-        <v>1492</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.2">
@@ -12280,10 +12289,10 @@
         <v>0</v>
       </c>
       <c r="B649" s="3" t="s">
-        <v>1411</v>
+        <v>1372</v>
       </c>
       <c r="C649" s="3" t="s">
-        <v>1412</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.2">
@@ -12291,7 +12300,7 @@
         <v>0</v>
       </c>
       <c r="C650" s="3" t="s">
-        <v>1508</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
@@ -12299,10 +12308,10 @@
         <v>0</v>
       </c>
       <c r="B651" s="3" t="s">
-        <v>1363</v>
+        <v>1411</v>
       </c>
       <c r="C651" s="3" t="s">
-        <v>1362</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.2">
@@ -12310,26 +12319,26 @@
         <v>0</v>
       </c>
       <c r="C652" s="3" t="s">
-        <v>1408</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A653" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B653" s="3" t="s">
-        <v>1519</v>
-      </c>
       <c r="C653" s="3" t="s">
-        <v>1520</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A654" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C654" s="19" t="s">
-        <v>1421</v>
+      <c r="B654" s="3" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C654" s="3" t="s">
+        <v>1362</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.2">
@@ -12337,7 +12346,7 @@
         <v>0</v>
       </c>
       <c r="C655" s="3" t="s">
-        <v>1525</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.2">
@@ -12345,29 +12354,48 @@
         <v>0</v>
       </c>
       <c r="C656" s="3" t="s">
-        <v>1526</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A657" s="15" t="s">
         <v>0</v>
       </c>
+      <c r="B657" s="3" t="s">
+        <v>1519</v>
+      </c>
       <c r="C657" s="3" t="s">
-        <v>1527</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A658" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C658" s="3" t="s">
-        <v>1528</v>
+      <c r="C658" s="19" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A659" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C659" s="3" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="660" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A660" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C660" s="3" t="s">
+        <v>1531</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C654">
-    <sortCondition ref="A2:A654"/>
-    <sortCondition ref="C2:C654"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C659">
+    <sortCondition ref="A2:A659"/>
+    <sortCondition ref="C2:C659"/>
   </sortState>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="containsText" dxfId="14" priority="10" operator="containsText" text="Submetido">

--- a/PPG/Produção.xlsx
+++ b/PPG/Produção.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBDE499E-1B5F-BB45-9E41-8F711F5A953C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{842202A1-9420-E94B-9DE7-B706E38B0C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="680" windowWidth="29340" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="900" yWindow="680" windowWidth="29340" windowHeight="18960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="artigos-completos" sheetId="4" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1570" uniqueCount="1532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="1537">
   <si>
     <t>Aceito</t>
   </si>
@@ -4642,6 +4642,21 @@
   </si>
   <si>
     <t>Associação entre o lócus de controle da dor e o risco de quedas em idosos com dor crônica: um estudo transversal de base comunitária</t>
+  </si>
+  <si>
+    <t>Crossfit® participants who experience reduced glenohumeral rotation movement and dynamic stability are more likely to report subacromial pain syndrome: A case‒control study</t>
+  </si>
+  <si>
+    <t>10.1016/j.jbmt.2026.03.029</t>
+  </si>
+  <si>
+    <t>10.1002/msc.70220</t>
+  </si>
+  <si>
+    <t>MUSCULAR, POSTURAL AND EMOTIONAL FACTORS ARE ASSOCIATED WITH Y-BALANCE TEST PERFORMANCE IN FEMALE WITH PATELLOFEMORAL PAIN?</t>
+  </si>
+  <si>
+    <t>10.1016/j.jbmt.2026.03.037</t>
   </si>
 </sst>
 </file>
@@ -5173,7 +5188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I660"/>
+  <dimension ref="A1:I662"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.140625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="15" bestFit="1" customWidth="1"/>
@@ -12342,8 +12357,11 @@
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A655" s="15" t="s">
-        <v>0</v>
+      <c r="A655" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B655" s="3" t="s">
+        <v>1534</v>
       </c>
       <c r="C655" s="3" t="s">
         <v>1528</v>
@@ -12390,6 +12408,28 @@
       </c>
       <c r="C660" s="3" t="s">
         <v>1531</v>
+      </c>
+    </row>
+    <row r="661" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A661" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B661" s="3" t="s">
+        <v>1533</v>
+      </c>
+      <c r="C661" s="3" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A662" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B662" s="3" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C662" s="3" t="s">
+        <v>1535</v>
       </c>
     </row>
   </sheetData>
@@ -12855,8 +12895,8 @@
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="s">
-        <v>0</v>
+      <c r="A39" s="3">
+        <v>2026</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>1511</v>

--- a/PPG/Produção.xlsx
+++ b/PPG/Produção.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{842202A1-9420-E94B-9DE7-B706E38B0C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64EC02E-C249-9D4D-BE6E-2588F77292D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="680" windowWidth="29340" windowHeight="18960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="900" yWindow="680" windowWidth="29340" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="artigos-completos" sheetId="4" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="trabalhos-anais" sheetId="8" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'artigos-completos'!$A$1:$C$614</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'artigos-completos'!$A$1:$C$664</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">editoração!$A$1:$C$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'trabalhos-anais'!$A$1:$C$38</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="1537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="1552">
   <si>
     <t>Aceito</t>
   </si>
@@ -4500,9 +4500,6 @@
     <t>10.3390/ijerph22121839</t>
   </si>
   <si>
-    <t>Assessment of Body Composition, Quality of Life, and Depression in Women with PCOS</t>
-  </si>
-  <si>
     <t xml:space="preserve">10.1371/journal.pone.0336898 </t>
   </si>
   <si>
@@ -4572,9 +4569,6 @@
     <t>10.3389/fmed.2026.1741129</t>
   </si>
   <si>
-    <t>Lócus de controle da saúde e sua associação com cinesiofobia, incapacidade e prognóstico na dor lombar crônica</t>
-  </si>
-  <si>
     <t xml:space="preserve">10.12865/CHSJ.51.04.10 </t>
   </si>
   <si>
@@ -4657,6 +4651,57 @@
   </si>
   <si>
     <t>10.1016/j.jbmt.2026.03.037</t>
+  </si>
+  <si>
+    <t>10.1016/j.ijosm.2026.100830</t>
+  </si>
+  <si>
+    <t>FATIGUE IN LONG COVID: AN EXPLORATORY PRAGMATIC RANDOMIZED TRIAL OF OSTEOPATHIC CARE PLUS PHYSICAL THERAPY VERSUS PHYSICAL THERAPY ALONE</t>
+  </si>
+  <si>
+    <t>DISEASE SEVERITY AND ITS ASSOCIATIONS WITH NON-ATAXIC SIGNS, COGNITION, MOBILITY, AND BALANCE IN SPINOCEREBELLAR ATAXIA: A CROSS-SECTIONAL STUDY: SCA SEVERITY AND OUTCOMES</t>
+  </si>
+  <si>
+    <t>10.20945/2359-4292-2026-0036</t>
+  </si>
+  <si>
+    <t>Assessment of body composition, quality of life, and depression in women with polycystic ovary syndrome</t>
+  </si>
+  <si>
+    <t>10.2478/advrehab-2026-0002</t>
+  </si>
+  <si>
+    <t>10.1016/j.jphys.2026.03.007</t>
+  </si>
+  <si>
+    <t>C5–C6 and thoracic spine mobilization with postural correction exercise compared with conventional therapy in patients with adhesive capsulitis: a two-group, parallel-arm, single-blinded, randomized clinical trial—study protocol</t>
+  </si>
+  <si>
+    <t>10.1186/s13063-026-09690-8</t>
+  </si>
+  <si>
+    <t>Immediate effects of self-massage compared to static stretching on neuromuscular and functional performance of physically active healthy adults: A crossover study</t>
+  </si>
+  <si>
+    <t>10.1016/j.jorep.2026.101049</t>
+  </si>
+  <si>
+    <t>Hand preference does not impact upright posture control during a reaching and grasping task: A cross-sectional study in healthy women</t>
+  </si>
+  <si>
+    <t>10.1177/19433654261447876</t>
+  </si>
+  <si>
+    <t>10.63231/2595-0118.202670-en</t>
+  </si>
+  <si>
+    <t>Health locus of control and its relationship with kinesiophobia, disability, and prognosis in chronic low back pain</t>
+  </si>
+  <si>
+    <t>Shoulder pain and disability predict clinical outcomes better than biomechanical and functional measures in young swimmers: a prospective cohort study</t>
+  </si>
+  <si>
+    <t>10.33155/ramd.v18i4.1246</t>
   </si>
 </sst>
 </file>
@@ -5188,7 +5233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I662"/>
+  <dimension ref="A1:I668"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.140625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="15" bestFit="1" customWidth="1"/>
@@ -11598,7 +11643,7 @@
         <v>2025</v>
       </c>
       <c r="B584" s="3" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="C584" s="3" t="s">
         <v>1467</v>
@@ -11609,10 +11654,10 @@
         <v>2025</v>
       </c>
       <c r="B585" s="3" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="C585" s="3" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="586" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -11774,10 +11819,10 @@
         <v>2025</v>
       </c>
       <c r="B600" s="3" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="C600" s="3" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.2">
@@ -11785,10 +11830,10 @@
         <v>2025</v>
       </c>
       <c r="B601" s="3" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="C601" s="3" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.2">
@@ -12082,10 +12127,10 @@
         <v>2025</v>
       </c>
       <c r="B628" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C628" s="3" t="s">
         <v>1490</v>
-      </c>
-      <c r="C628" s="3" t="s">
-        <v>1491</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
@@ -12115,10 +12160,10 @@
         <v>2025</v>
       </c>
       <c r="B631" s="3" t="s">
-        <v>1327</v>
+        <v>1551</v>
       </c>
       <c r="C631" s="3" t="s">
-        <v>1322</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.2">
@@ -12126,10 +12171,10 @@
         <v>2025</v>
       </c>
       <c r="B632" s="3" t="s">
-        <v>1358</v>
+        <v>1327</v>
       </c>
       <c r="C632" s="3" t="s">
-        <v>1353</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.2">
@@ -12137,10 +12182,10 @@
         <v>2025</v>
       </c>
       <c r="B633" s="3" t="s">
-        <v>1425</v>
+        <v>1358</v>
       </c>
       <c r="C633" s="3" t="s">
-        <v>1424</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.2">
@@ -12148,21 +12193,21 @@
         <v>2025</v>
       </c>
       <c r="B634" s="3" t="s">
-        <v>1355</v>
+        <v>1425</v>
       </c>
       <c r="C634" s="3" t="s">
-        <v>1339</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A635" s="15">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B635" s="3" t="s">
-        <v>1493</v>
+        <v>1355</v>
       </c>
       <c r="C635" s="3" t="s">
-        <v>1486</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="636" spans="1:3" x14ac:dyDescent="0.2">
@@ -12170,10 +12215,10 @@
         <v>2026</v>
       </c>
       <c r="B636" s="3" t="s">
-        <v>1507</v>
+        <v>1540</v>
       </c>
       <c r="C636" s="3" t="s">
-        <v>1495</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.2">
@@ -12181,10 +12226,10 @@
         <v>2026</v>
       </c>
       <c r="B637" s="3" t="s">
-        <v>1499</v>
+        <v>1538</v>
       </c>
       <c r="C637" s="3" t="s">
-        <v>1498</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.2">
@@ -12192,10 +12237,10 @@
         <v>2026</v>
       </c>
       <c r="B638" s="3" t="s">
-        <v>1420</v>
+        <v>1543</v>
       </c>
       <c r="C638" s="3" t="s">
-        <v>1419</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.2">
@@ -12203,10 +12248,10 @@
         <v>2026</v>
       </c>
       <c r="B639" s="3" t="s">
-        <v>1496</v>
+        <v>1531</v>
       </c>
       <c r="C639" s="3" t="s">
-        <v>1497</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
@@ -12214,10 +12259,10 @@
         <v>2026</v>
       </c>
       <c r="B640" s="3" t="s">
-        <v>1504</v>
+        <v>1411</v>
       </c>
       <c r="C640" s="3" t="s">
-        <v>1505</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.2">
@@ -12225,10 +12270,10 @@
         <v>2026</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>1517</v>
+        <v>1492</v>
       </c>
       <c r="C641" s="3" t="s">
-        <v>1518</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.2">
@@ -12236,10 +12281,10 @@
         <v>2026</v>
       </c>
       <c r="B642" s="3" t="s">
-        <v>1524</v>
+        <v>1506</v>
       </c>
       <c r="C642" s="3" t="s">
-        <v>1523</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.2">
@@ -12247,10 +12292,10 @@
         <v>2026</v>
       </c>
       <c r="B643" s="3" t="s">
-        <v>1409</v>
+        <v>1535</v>
       </c>
       <c r="C643" s="3" t="s">
-        <v>1410</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.2">
@@ -12258,10 +12303,10 @@
         <v>2026</v>
       </c>
       <c r="B644" s="3" t="s">
-        <v>1529</v>
+        <v>1548</v>
       </c>
       <c r="C644" s="3" t="s">
-        <v>1530</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.2">
@@ -12269,91 +12314,109 @@
         <v>2026</v>
       </c>
       <c r="B645" s="3" t="s">
-        <v>1489</v>
+        <v>1498</v>
       </c>
       <c r="C645" s="3" t="s">
-        <v>1426</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A646" s="15" t="s">
-        <v>0</v>
+      <c r="A646" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B646" s="3" t="s">
+        <v>1541</v>
       </c>
       <c r="C646" s="3" t="s">
-        <v>1488</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A647" s="15" t="s">
-        <v>0</v>
+      <c r="A647" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B647" s="3" t="s">
+        <v>1363</v>
       </c>
       <c r="C647" s="3" t="s">
-        <v>1484</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A648" s="15" t="s">
-        <v>0</v>
+      <c r="A648" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B648" s="3" t="s">
+        <v>1534</v>
       </c>
       <c r="C648" s="3" t="s">
-        <v>1237</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A649" s="15" t="s">
-        <v>0</v>
+      <c r="A649" s="15">
+        <v>2026</v>
       </c>
       <c r="B649" s="3" t="s">
-        <v>1372</v>
+        <v>1420</v>
       </c>
       <c r="C649" s="3" t="s">
-        <v>1492</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A650" s="15" t="s">
-        <v>0</v>
+      <c r="A650" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B650" s="3" t="s">
+        <v>1532</v>
       </c>
       <c r="C650" s="3" t="s">
         <v>1526</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A651" s="15" t="s">
-        <v>0</v>
+      <c r="A651" s="15">
+        <v>2026</v>
       </c>
       <c r="B651" s="3" t="s">
-        <v>1411</v>
+        <v>1495</v>
       </c>
       <c r="C651" s="3" t="s">
-        <v>1412</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A652" s="15" t="s">
-        <v>0</v>
+      <c r="A652" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B652" s="3" t="s">
+        <v>1503</v>
       </c>
       <c r="C652" s="3" t="s">
-        <v>1527</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A653" s="15" t="s">
-        <v>0</v>
+      <c r="A653" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B653" s="3" t="s">
+        <v>1515</v>
       </c>
       <c r="C653" s="3" t="s">
-        <v>1508</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A654" s="15" t="s">
-        <v>0</v>
+      <c r="A654" s="15">
+        <v>2026</v>
       </c>
       <c r="B654" s="3" t="s">
-        <v>1363</v>
+        <v>1522</v>
       </c>
       <c r="C654" s="3" t="s">
-        <v>1362</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.2">
@@ -12361,37 +12424,40 @@
         <v>2026</v>
       </c>
       <c r="B655" s="3" t="s">
-        <v>1534</v>
+        <v>1409</v>
       </c>
       <c r="C655" s="3" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A656" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B656" s="3" t="s">
+        <v>1527</v>
+      </c>
+      <c r="C656" s="3" t="s">
         <v>1528</v>
       </c>
     </row>
-    <row r="656" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A656" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C656" s="3" t="s">
-        <v>1408</v>
-      </c>
-    </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A657" s="15" t="s">
-        <v>0</v>
+      <c r="A657" s="15">
+        <v>2026</v>
       </c>
       <c r="B657" s="3" t="s">
-        <v>1519</v>
+        <v>1488</v>
       </c>
       <c r="C657" s="3" t="s">
-        <v>1520</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A658" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C658" s="19" t="s">
-        <v>1421</v>
+      <c r="C658" s="3" t="s">
+        <v>1529</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.2">
@@ -12399,15 +12465,18 @@
         <v>0</v>
       </c>
       <c r="C659" s="3" t="s">
-        <v>1525</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="660" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A660" s="15" t="s">
         <v>0</v>
       </c>
+      <c r="B660" s="3" t="s">
+        <v>1372</v>
+      </c>
       <c r="C660" s="3" t="s">
-        <v>1531</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.2">
@@ -12415,27 +12484,78 @@
         <v>0</v>
       </c>
       <c r="B661" s="3" t="s">
-        <v>1533</v>
+        <v>1547</v>
       </c>
       <c r="C661" s="3" t="s">
-        <v>1532</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B662" s="3" t="s">
-        <v>1536</v>
-      </c>
       <c r="C662" s="3" t="s">
-        <v>1535</v>
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A663" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C663" s="3" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="664" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A664" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B664" s="3" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C664" s="3" t="s">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A665" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C665" s="3" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A666" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B666" s="3" t="s">
+        <v>1517</v>
+      </c>
+      <c r="C666" s="3" t="s">
+        <v>1518</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A667" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C667" s="19" t="s">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A668" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C668" s="3" t="s">
+        <v>1523</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C659">
-    <sortCondition ref="A2:A659"/>
-    <sortCondition ref="C2:C659"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C668">
+    <sortCondition ref="A2:A668"/>
+    <sortCondition ref="C2:C668"/>
   </sortState>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="containsText" dxfId="14" priority="10" operator="containsText" text="Submetido">
@@ -12453,10 +12573,10 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B633:B1048576 B1:B630 C631">
+  <conditionalFormatting sqref="B633:B667 B669:B1048576 C668 B1:B630 C631">
     <cfRule type="duplicateValues" dxfId="12" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C633:C1048576 C1:C630">
+  <conditionalFormatting sqref="C633:C667 C669:C1048576 C1:C630">
     <cfRule type="duplicateValues" dxfId="11" priority="1"/>
   </conditionalFormatting>
   <hyperlinks>
@@ -12888,10 +13008,10 @@
         <v>2026</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -12899,10 +13019,10 @@
         <v>2026</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -12910,10 +13030,10 @@
         <v>2026</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
@@ -12921,10 +13041,10 @@
         <v>2026</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
     </row>
   </sheetData>
@@ -14677,7 +14797,7 @@
         <v>2025</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
@@ -14685,7 +14805,7 @@
         <v>2025</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
@@ -14693,7 +14813,7 @@
         <v>2025</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
     </row>
   </sheetData>

--- a/PPG/Produção.xlsx
+++ b/PPG/Produção.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64EC02E-C249-9D4D-BE6E-2588F77292D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{235390FC-3E1B-9249-9283-E51BDB05F75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="900" yWindow="680" windowWidth="29340" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="1552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="1553">
   <si>
     <t>Aceito</t>
   </si>
@@ -4311,9 +4311,6 @@
     <t>10.1016/j.bjpt.2025.101262</t>
   </si>
   <si>
-    <t>Predictors of the six-minute walking distance in patients with post-tuberculosis lung disease</t>
-  </si>
-  <si>
     <t>10.36416/1806-3756/e20240312</t>
   </si>
   <si>
@@ -4702,6 +4699,12 @@
   </si>
   <si>
     <t>10.33155/ramd.v18i4.1246</t>
+  </si>
+  <si>
+    <t>Predictors of the 6-minute walking distance in patients with post-tuberculosis lung disease</t>
+  </si>
+  <si>
+    <t>10.5588/ijtldcrd.25.0536</t>
   </si>
 </sst>
 </file>
@@ -11643,10 +11646,10 @@
         <v>2025</v>
       </c>
       <c r="B584" s="3" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="C584" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
@@ -11654,10 +11657,10 @@
         <v>2025</v>
       </c>
       <c r="B585" s="3" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C585" s="3" t="s">
         <v>1507</v>
-      </c>
-      <c r="C585" s="3" t="s">
-        <v>1508</v>
       </c>
     </row>
     <row r="586" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -11698,10 +11701,10 @@
         <v>2025</v>
       </c>
       <c r="B589" s="3" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="C589" s="3" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.2">
@@ -11808,10 +11811,10 @@
         <v>2025</v>
       </c>
       <c r="B599" s="3" t="s">
+        <v>1469</v>
+      </c>
+      <c r="C599" s="3" t="s">
         <v>1470</v>
-      </c>
-      <c r="C599" s="3" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.2">
@@ -11819,10 +11822,10 @@
         <v>2025</v>
       </c>
       <c r="B600" s="3" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="C600" s="3" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.2">
@@ -11830,10 +11833,10 @@
         <v>2025</v>
       </c>
       <c r="B601" s="3" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="C601" s="3" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.2">
@@ -11841,10 +11844,10 @@
         <v>2025</v>
       </c>
       <c r="B602" s="3" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="C602" s="3" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.2">
@@ -11907,7 +11910,7 @@
         <v>2025</v>
       </c>
       <c r="B608" s="3" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="C608" s="3" t="s">
         <v>1403</v>
@@ -12072,10 +12075,10 @@
         <v>2025</v>
       </c>
       <c r="B623" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="C623" s="3" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.2">
@@ -12116,10 +12119,10 @@
         <v>2025</v>
       </c>
       <c r="B627" s="3" t="s">
+        <v>1421</v>
+      </c>
+      <c r="C627" s="3" t="s">
         <v>1422</v>
-      </c>
-      <c r="C627" s="3" t="s">
-        <v>1423</v>
       </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.2">
@@ -12127,10 +12130,10 @@
         <v>2025</v>
       </c>
       <c r="B628" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C628" s="3" t="s">
         <v>1489</v>
-      </c>
-      <c r="C628" s="3" t="s">
-        <v>1490</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
@@ -12138,7 +12141,7 @@
         <v>2025</v>
       </c>
       <c r="B629" s="3" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="C629" s="3" t="s">
         <v>1402</v>
@@ -12160,10 +12163,10 @@
         <v>2025</v>
       </c>
       <c r="B631" s="3" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="C631" s="3" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.2">
@@ -12193,10 +12196,10 @@
         <v>2025</v>
       </c>
       <c r="B634" s="3" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="C634" s="3" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="635" spans="1:3" x14ac:dyDescent="0.2">
@@ -12215,10 +12218,10 @@
         <v>2026</v>
       </c>
       <c r="B636" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="C636" s="3" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.2">
@@ -12226,10 +12229,10 @@
         <v>2026</v>
       </c>
       <c r="B637" s="3" t="s">
+        <v>1537</v>
+      </c>
+      <c r="C637" s="3" t="s">
         <v>1538</v>
-      </c>
-      <c r="C637" s="3" t="s">
-        <v>1539</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.2">
@@ -12237,10 +12240,10 @@
         <v>2026</v>
       </c>
       <c r="B638" s="3" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="C638" s="3" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.2">
@@ -12248,10 +12251,10 @@
         <v>2026</v>
       </c>
       <c r="B639" s="3" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="C639" s="3" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
@@ -12270,10 +12273,10 @@
         <v>2026</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="C641" s="3" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.2">
@@ -12281,10 +12284,10 @@
         <v>2026</v>
       </c>
       <c r="B642" s="3" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="C642" s="3" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.2">
@@ -12292,10 +12295,10 @@
         <v>2026</v>
       </c>
       <c r="B643" s="3" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C643" s="3" t="s">
         <v>1535</v>
-      </c>
-      <c r="C643" s="3" t="s">
-        <v>1536</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.2">
@@ -12303,10 +12306,10 @@
         <v>2026</v>
       </c>
       <c r="B644" s="3" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C644" s="3" t="s">
         <v>1548</v>
-      </c>
-      <c r="C644" s="3" t="s">
-        <v>1549</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.2">
@@ -12314,10 +12317,10 @@
         <v>2026</v>
       </c>
       <c r="B645" s="3" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="C645" s="3" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.2">
@@ -12325,10 +12328,10 @@
         <v>2026</v>
       </c>
       <c r="B646" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="C646" s="3" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.2">
@@ -12347,10 +12350,10 @@
         <v>2026</v>
       </c>
       <c r="B648" s="3" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="C648" s="3" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.2">
@@ -12369,10 +12372,10 @@
         <v>2026</v>
       </c>
       <c r="B650" s="3" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C650" s="3" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
@@ -12380,10 +12383,10 @@
         <v>2026</v>
       </c>
       <c r="B651" s="3" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C651" s="3" t="s">
         <v>1495</v>
-      </c>
-      <c r="C651" s="3" t="s">
-        <v>1496</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.2">
@@ -12391,10 +12394,10 @@
         <v>2026</v>
       </c>
       <c r="B652" s="3" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C652" s="3" t="s">
         <v>1503</v>
-      </c>
-      <c r="C652" s="3" t="s">
-        <v>1504</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.2">
@@ -12402,10 +12405,10 @@
         <v>2026</v>
       </c>
       <c r="B653" s="3" t="s">
+        <v>1514</v>
+      </c>
+      <c r="C653" s="3" t="s">
         <v>1515</v>
-      </c>
-      <c r="C653" s="3" t="s">
-        <v>1516</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.2">
@@ -12413,10 +12416,10 @@
         <v>2026</v>
       </c>
       <c r="B654" s="3" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="C654" s="3" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.2">
@@ -12435,10 +12438,10 @@
         <v>2026</v>
       </c>
       <c r="B656" s="3" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C656" s="3" t="s">
         <v>1527</v>
-      </c>
-      <c r="C656" s="3" t="s">
-        <v>1528</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.2">
@@ -12446,10 +12449,10 @@
         <v>2026</v>
       </c>
       <c r="B657" s="3" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="C657" s="3" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.2">
@@ -12457,7 +12460,7 @@
         <v>0</v>
       </c>
       <c r="C658" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="659" spans="1:3" x14ac:dyDescent="0.2">
@@ -12476,7 +12479,7 @@
         <v>1372</v>
       </c>
       <c r="C660" s="3" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.2">
@@ -12484,10 +12487,10 @@
         <v>0</v>
       </c>
       <c r="B661" s="3" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="C661" s="3" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
@@ -12495,7 +12498,7 @@
         <v>0</v>
       </c>
       <c r="C662" s="3" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.2">
@@ -12503,7 +12506,7 @@
         <v>0</v>
       </c>
       <c r="C663" s="3" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.2">
@@ -12511,10 +12514,10 @@
         <v>0</v>
       </c>
       <c r="B664" s="3" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="C664" s="3" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.2">
@@ -12530,18 +12533,21 @@
         <v>0</v>
       </c>
       <c r="B666" s="3" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C666" s="3" t="s">
         <v>1517</v>
       </c>
-      <c r="C666" s="3" t="s">
-        <v>1518</v>
-      </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A667" s="15" t="s">
-        <v>0</v>
+      <c r="A667" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B667" s="3" t="s">
+        <v>1552</v>
       </c>
       <c r="C667" s="19" t="s">
-        <v>1421</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.2">
@@ -12549,7 +12555,7 @@
         <v>0</v>
       </c>
       <c r="C668" s="3" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
     </row>
   </sheetData>
@@ -13008,10 +13014,10 @@
         <v>2026</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -13019,10 +13025,10 @@
         <v>2026</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -13030,10 +13036,10 @@
         <v>2026</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
@@ -13041,10 +13047,10 @@
         <v>2026</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
     </row>
   </sheetData>
@@ -13167,10 +13173,10 @@
         <v>2025</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -13178,10 +13184,10 @@
         <v>2025</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>1477</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>1478</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -14566,10 +14572,10 @@
         <v>2025</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -14577,10 +14583,10 @@
         <v>2025</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>1432</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>1433</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
@@ -14588,10 +14594,10 @@
         <v>2025</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>1434</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>1435</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
@@ -14599,10 +14605,10 @@
         <v>2025</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
@@ -14610,10 +14616,10 @@
         <v>2025</v>
       </c>
       <c r="B69" s="3" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>1438</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>1439</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
@@ -14621,10 +14627,10 @@
         <v>2025</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
@@ -14632,10 +14638,10 @@
         <v>2025</v>
       </c>
       <c r="B71" s="3" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>1442</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>1443</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
@@ -14643,10 +14649,10 @@
         <v>2025</v>
       </c>
       <c r="B72" s="3" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>1444</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
@@ -14654,10 +14660,10 @@
         <v>2025</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
@@ -14665,10 +14671,10 @@
         <v>2025</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
@@ -14676,10 +14682,10 @@
         <v>2025</v>
       </c>
       <c r="B75" s="3" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>1450</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>1451</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
@@ -14687,10 +14693,10 @@
         <v>2025</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
@@ -14698,10 +14704,10 @@
         <v>2025</v>
       </c>
       <c r="B77" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>1454</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>1455</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
@@ -14709,10 +14715,10 @@
         <v>2025</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
@@ -14720,10 +14726,10 @@
         <v>2025</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>1457</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>1458</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>1459</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
@@ -14731,10 +14737,10 @@
         <v>2025</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
@@ -14742,10 +14748,10 @@
         <v>2025</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>1462</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>1463</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
@@ -14753,10 +14759,10 @@
         <v>2025</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
@@ -14764,10 +14770,10 @@
         <v>2025</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
@@ -14775,10 +14781,10 @@
         <v>2025</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
@@ -14786,10 +14792,10 @@
         <v>2025</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
@@ -14797,7 +14803,7 @@
         <v>2025</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
@@ -14805,7 +14811,7 @@
         <v>2025</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
@@ -14813,7 +14819,7 @@
         <v>2025</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
     </row>
   </sheetData>

--- a/PPG/Produção.xlsx
+++ b/PPG/Produção.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{235390FC-3E1B-9249-9283-E51BDB05F75E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ADDE091-310D-364D-AC4E-AEBD6A6E102B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="900" yWindow="680" windowWidth="29340" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="1553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="1557">
   <si>
     <t>Aceito</t>
   </si>
@@ -4614,9 +4614,6 @@
     <t>10.25248/REAS.e23124.2026</t>
   </si>
   <si>
-    <t>Translation, cross-cultural adaptation, and measurement properties of the Back pain Knowledge and beliefs Survey (BacKS) for the Brazilian population</t>
-  </si>
-  <si>
     <t>Development and Validation of the Respiratory Secretion Scale (RESES) in Mechanically Ventilated Patients</t>
   </si>
   <si>
@@ -4705,6 +4702,21 @@
   </si>
   <si>
     <t>10.5588/ijtldcrd.25.0536</t>
+  </si>
+  <si>
+    <t>10.32098/mltj_2026_7106</t>
+  </si>
+  <si>
+    <t>10.12688/f1000research.180073.1</t>
+  </si>
+  <si>
+    <t>Effect of high-intensity interval training (HIIT) versus moderate-intensity continuous training (MICT) on insulin sensitivity in participants with type 2 diabetes mellitus (T2DM): A systematic review and meta-analysis of randomised controlled trials [version 1; peer review: awaiting peer review</t>
+  </si>
+  <si>
+    <t>Translation, cross-cultural adaptation, and measurement properties of the Back pain knowledge and beliefs survey (BacKS) for the Brazilian population</t>
+  </si>
+  <si>
+    <t>10.1016/j.bjpt.2026.101600</t>
   </si>
 </sst>
 </file>
@@ -5236,7 +5248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I668"/>
+  <dimension ref="A1:I669"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.140625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="15" bestFit="1" customWidth="1"/>
@@ -12163,10 +12175,10 @@
         <v>2025</v>
       </c>
       <c r="B631" s="3" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="C631" s="3" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.2">
@@ -12218,7 +12230,7 @@
         <v>2026</v>
       </c>
       <c r="B636" s="3" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="C636" s="3" t="s">
         <v>1486</v>
@@ -12229,10 +12241,10 @@
         <v>2026</v>
       </c>
       <c r="B637" s="3" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C637" s="3" t="s">
         <v>1537</v>
-      </c>
-      <c r="C637" s="3" t="s">
-        <v>1538</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.2">
@@ -12240,10 +12252,10 @@
         <v>2026</v>
       </c>
       <c r="B638" s="3" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="C638" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.2">
@@ -12251,10 +12263,10 @@
         <v>2026</v>
       </c>
       <c r="B639" s="3" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="C639" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
@@ -12273,10 +12285,10 @@
         <v>2026</v>
       </c>
       <c r="B641" s="3" t="s">
-        <v>1491</v>
+        <v>1553</v>
       </c>
       <c r="C641" s="3" t="s">
-        <v>1484</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.2">
@@ -12284,10 +12296,10 @@
         <v>2026</v>
       </c>
       <c r="B642" s="3" t="s">
-        <v>1505</v>
+        <v>1491</v>
       </c>
       <c r="C642" s="3" t="s">
-        <v>1493</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.2">
@@ -12295,10 +12307,10 @@
         <v>2026</v>
       </c>
       <c r="B643" s="3" t="s">
-        <v>1534</v>
+        <v>1505</v>
       </c>
       <c r="C643" s="3" t="s">
-        <v>1535</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="644" spans="1:3" x14ac:dyDescent="0.2">
@@ -12306,10 +12318,10 @@
         <v>2026</v>
       </c>
       <c r="B644" s="3" t="s">
-        <v>1547</v>
+        <v>1533</v>
       </c>
       <c r="C644" s="3" t="s">
-        <v>1548</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.2">
@@ -12317,10 +12329,10 @@
         <v>2026</v>
       </c>
       <c r="B645" s="3" t="s">
-        <v>1497</v>
+        <v>1546</v>
       </c>
       <c r="C645" s="3" t="s">
-        <v>1496</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.2">
@@ -12328,10 +12340,10 @@
         <v>2026</v>
       </c>
       <c r="B646" s="3" t="s">
-        <v>1540</v>
+        <v>1497</v>
       </c>
       <c r="C646" s="3" t="s">
-        <v>1524</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.2">
@@ -12339,10 +12351,10 @@
         <v>2026</v>
       </c>
       <c r="B647" s="3" t="s">
-        <v>1363</v>
+        <v>1539</v>
       </c>
       <c r="C647" s="3" t="s">
-        <v>1362</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.2">
@@ -12350,10 +12362,10 @@
         <v>2026</v>
       </c>
       <c r="B648" s="3" t="s">
-        <v>1533</v>
+        <v>1363</v>
       </c>
       <c r="C648" s="3" t="s">
-        <v>1532</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.2">
@@ -12361,10 +12373,10 @@
         <v>2026</v>
       </c>
       <c r="B649" s="3" t="s">
-        <v>1420</v>
+        <v>1532</v>
       </c>
       <c r="C649" s="3" t="s">
-        <v>1419</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.2">
@@ -12372,10 +12384,10 @@
         <v>2026</v>
       </c>
       <c r="B650" s="3" t="s">
-        <v>1531</v>
+        <v>1420</v>
       </c>
       <c r="C650" s="3" t="s">
-        <v>1525</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
@@ -12383,10 +12395,10 @@
         <v>2026</v>
       </c>
       <c r="B651" s="3" t="s">
-        <v>1494</v>
+        <v>1530</v>
       </c>
       <c r="C651" s="3" t="s">
-        <v>1495</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.2">
@@ -12394,10 +12406,10 @@
         <v>2026</v>
       </c>
       <c r="B652" s="3" t="s">
-        <v>1502</v>
+        <v>1494</v>
       </c>
       <c r="C652" s="3" t="s">
-        <v>1503</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="653" spans="1:3" x14ac:dyDescent="0.2">
@@ -12405,10 +12417,10 @@
         <v>2026</v>
       </c>
       <c r="B653" s="3" t="s">
-        <v>1514</v>
+        <v>1552</v>
       </c>
       <c r="C653" s="3" t="s">
-        <v>1515</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="654" spans="1:3" x14ac:dyDescent="0.2">
@@ -12416,10 +12428,10 @@
         <v>2026</v>
       </c>
       <c r="B654" s="3" t="s">
-        <v>1521</v>
-      </c>
-      <c r="C654" s="3" t="s">
-        <v>1520</v>
+        <v>1551</v>
+      </c>
+      <c r="C654" s="19" t="s">
+        <v>1550</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.2">
@@ -12427,10 +12439,10 @@
         <v>2026</v>
       </c>
       <c r="B655" s="3" t="s">
-        <v>1409</v>
+        <v>1502</v>
       </c>
       <c r="C655" s="3" t="s">
-        <v>1410</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="656" spans="1:3" x14ac:dyDescent="0.2">
@@ -12438,10 +12450,10 @@
         <v>2026</v>
       </c>
       <c r="B656" s="3" t="s">
-        <v>1526</v>
+        <v>1514</v>
       </c>
       <c r="C656" s="3" t="s">
-        <v>1527</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="657" spans="1:3" x14ac:dyDescent="0.2">
@@ -12449,48 +12461,54 @@
         <v>2026</v>
       </c>
       <c r="B657" s="3" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C657" s="3" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A658" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B658" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C658" s="3" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A659" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B659" s="3" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C659" s="3" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="660" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A660" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B660" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C660" s="3" t="s">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="661" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A661" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B661" s="3" t="s">
         <v>1487</v>
       </c>
-      <c r="C657" s="3" t="s">
+      <c r="C661" s="3" t="s">
         <v>1425</v>
-      </c>
-    </row>
-    <row r="658" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A658" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C658" s="3" t="s">
-        <v>1528</v>
-      </c>
-    </row>
-    <row r="659" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A659" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C659" s="3" t="s">
-        <v>1237</v>
-      </c>
-    </row>
-    <row r="660" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A660" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B660" s="3" t="s">
-        <v>1372</v>
-      </c>
-      <c r="C660" s="3" t="s">
-        <v>1490</v>
-      </c>
-    </row>
-    <row r="661" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A661" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B661" s="3" t="s">
-        <v>1546</v>
-      </c>
-      <c r="C661" s="3" t="s">
-        <v>1523</v>
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
@@ -12498,7 +12516,7 @@
         <v>0</v>
       </c>
       <c r="C662" s="3" t="s">
-        <v>1536</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.2">
@@ -12506,7 +12524,7 @@
         <v>0</v>
       </c>
       <c r="C663" s="3" t="s">
-        <v>1545</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.2">
@@ -12514,54 +12532,65 @@
         <v>0</v>
       </c>
       <c r="B664" s="3" t="s">
-        <v>1544</v>
+        <v>1372</v>
       </c>
       <c r="C664" s="3" t="s">
-        <v>1543</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="665" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A665" s="15" t="s">
         <v>0</v>
       </c>
+      <c r="B665" s="3" t="s">
+        <v>1545</v>
+      </c>
       <c r="C665" s="3" t="s">
-        <v>1408</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="666" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A666" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B666" s="3" t="s">
-        <v>1516</v>
-      </c>
       <c r="C666" s="3" t="s">
-        <v>1517</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A667" s="15">
-        <v>2026</v>
-      </c>
-      <c r="B667" s="3" t="s">
-        <v>1552</v>
-      </c>
-      <c r="C667" s="19" t="s">
-        <v>1551</v>
+      <c r="A667" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C667" s="3" t="s">
+        <v>1544</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A668" s="15" t="s">
         <v>0</v>
       </c>
+      <c r="B668" s="3" t="s">
+        <v>1543</v>
+      </c>
       <c r="C668" s="3" t="s">
-        <v>1522</v>
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="669" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A669" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B669" s="3" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C669" s="3" t="s">
+        <v>1517</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C668">
-    <sortCondition ref="A2:A668"/>
-    <sortCondition ref="C2:C668"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C669">
+    <sortCondition ref="A2:A669"/>
+    <sortCondition ref="C2:C669"/>
   </sortState>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="containsText" dxfId="14" priority="10" operator="containsText" text="Submetido">

--- a/PPG/Produção.xlsx
+++ b/PPG/Produção.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ADDE091-310D-364D-AC4E-AEBD6A6E102B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A418B65F-5BC7-FF48-9951-11273A71A46B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="900" yWindow="680" windowWidth="29340" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="1557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="1564">
   <si>
     <t>Aceito</t>
   </si>
@@ -4629,9 +4629,6 @@
     <t>The Relationship Between Psychological Factors and Postural Performance under Different Biofeedback Conditions</t>
   </si>
   <si>
-    <t>Associação entre o lócus de controle da dor e o risco de quedas em idosos com dor crônica: um estudo transversal de base comunitária</t>
-  </si>
-  <si>
     <t>Crossfit® participants who experience reduced glenohumeral rotation movement and dynamic stability are more likely to report subacromial pain syndrome: A case‒control study</t>
   </si>
   <si>
@@ -4717,6 +4714,30 @@
   </si>
   <si>
     <t>10.1016/j.bjpt.2026.101600</t>
+  </si>
+  <si>
+    <t>Cross-cultural validation of the Mazzarolo Music Performance Anxiety Scale - Brazilian Version (M-MPAS-Br)</t>
+  </si>
+  <si>
+    <t>10.20338/bjmb.v20i1.520</t>
+  </si>
+  <si>
+    <t>Treatment strategies and clinical outcomes in shrinking lung syndrome in systemic lupus erythematosus: An updated systematic review</t>
+  </si>
+  <si>
+    <t>Musculoskeletal pain, performance anxiety, and stress-producing life events among orchestral players in Brazil: an observational study</t>
+  </si>
+  <si>
+    <t>Effects of Systemic Vibratory Therapy Combined With a Physical Activity Program in Older Adults on Fall Risk, Balance, Physical Conditioning, and Neuromuscular Variables: Study Protocol for a Randomised Controlled Trial</t>
+  </si>
+  <si>
+    <t>10.63231/2595-0118.202673-en</t>
+  </si>
+  <si>
+    <t>Association between pain locus of control and fall risk in older adults with chronic pain: community-based cross-sectional study</t>
+  </si>
+  <si>
+    <t>Temporal trends (2006-2019) regarding physical activity among adolescents living in the city of Rio de Janeiro, Brazil</t>
   </si>
 </sst>
 </file>
@@ -5248,7 +5269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I669"/>
+  <dimension ref="A1:I674"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.140625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="15" bestFit="1" customWidth="1"/>
@@ -12175,10 +12196,10 @@
         <v>2025</v>
       </c>
       <c r="B631" s="3" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="C631" s="3" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="632" spans="1:3" x14ac:dyDescent="0.2">
@@ -12230,7 +12251,7 @@
         <v>2026</v>
       </c>
       <c r="B636" s="3" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="C636" s="3" t="s">
         <v>1486</v>
@@ -12241,10 +12262,10 @@
         <v>2026</v>
       </c>
       <c r="B637" s="3" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C637" s="3" t="s">
         <v>1536</v>
-      </c>
-      <c r="C637" s="3" t="s">
-        <v>1537</v>
       </c>
     </row>
     <row r="638" spans="1:3" x14ac:dyDescent="0.2">
@@ -12252,10 +12273,10 @@
         <v>2026</v>
       </c>
       <c r="B638" s="3" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="C638" s="3" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.2">
@@ -12263,10 +12284,10 @@
         <v>2026</v>
       </c>
       <c r="B639" s="3" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="C639" s="3" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
@@ -12285,10 +12306,10 @@
         <v>2026</v>
       </c>
       <c r="B641" s="3" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C641" s="3" t="s">
         <v>1553</v>
-      </c>
-      <c r="C641" s="3" t="s">
-        <v>1554</v>
       </c>
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.2">
@@ -12318,10 +12339,10 @@
         <v>2026</v>
       </c>
       <c r="B644" s="3" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C644" s="3" t="s">
         <v>1533</v>
-      </c>
-      <c r="C644" s="3" t="s">
-        <v>1534</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.2">
@@ -12329,10 +12350,10 @@
         <v>2026</v>
       </c>
       <c r="B645" s="3" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C645" s="3" t="s">
         <v>1546</v>
-      </c>
-      <c r="C645" s="3" t="s">
-        <v>1547</v>
       </c>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.2">
@@ -12351,7 +12372,7 @@
         <v>2026</v>
       </c>
       <c r="B647" s="3" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="C647" s="3" t="s">
         <v>1523</v>
@@ -12373,10 +12394,10 @@
         <v>2026</v>
       </c>
       <c r="B649" s="3" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="C649" s="3" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.2">
@@ -12395,7 +12416,7 @@
         <v>2026</v>
       </c>
       <c r="B651" s="3" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="C651" s="3" t="s">
         <v>1524</v>
@@ -12417,7 +12438,7 @@
         <v>2026</v>
       </c>
       <c r="B653" s="3" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="C653" s="3" t="s">
         <v>1408</v>
@@ -12428,10 +12449,10 @@
         <v>2026</v>
       </c>
       <c r="B654" s="3" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="C654" s="19" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.2">
@@ -12494,10 +12515,10 @@
         <v>2026</v>
       </c>
       <c r="B660" s="3" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="C660" s="3" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.2">
@@ -12512,11 +12533,14 @@
       </c>
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A662" s="15" t="s">
-        <v>0</v>
+      <c r="A662" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B662" s="3" t="s">
+        <v>1561</v>
       </c>
       <c r="C662" s="3" t="s">
-        <v>1527</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="663" spans="1:3" x14ac:dyDescent="0.2">
@@ -12543,7 +12567,7 @@
         <v>0</v>
       </c>
       <c r="B665" s="3" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="C665" s="3" t="s">
         <v>1522</v>
@@ -12554,15 +12578,18 @@
         <v>0</v>
       </c>
       <c r="C666" s="3" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A667" s="15" t="s">
         <v>0</v>
       </c>
+      <c r="B667" s="3" t="s">
+        <v>1542</v>
+      </c>
       <c r="C667" s="3" t="s">
-        <v>1544</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="668" spans="1:3" x14ac:dyDescent="0.2">
@@ -12570,27 +12597,67 @@
         <v>0</v>
       </c>
       <c r="B668" s="3" t="s">
-        <v>1543</v>
+        <v>1516</v>
       </c>
       <c r="C668" s="3" t="s">
-        <v>1542</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="669" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A669" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B669" s="3" t="s">
-        <v>1516</v>
-      </c>
       <c r="C669" s="3" t="s">
-        <v>1517</v>
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A670" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B670" s="3" t="s">
+        <v>1557</v>
+      </c>
+      <c r="C670" s="3" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="671" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A671" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C671" s="3" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="672" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A672" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C672" s="3" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="673" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A673" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C673" s="3" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A674" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C674" s="3" t="s">
+        <v>1563</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C669">
-    <sortCondition ref="A2:A669"/>
-    <sortCondition ref="C2:C669"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C668">
+    <sortCondition ref="A2:A668"/>
+    <sortCondition ref="C2:C668"/>
   </sortState>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="containsText" dxfId="14" priority="10" operator="containsText" text="Submetido">
@@ -12608,11 +12675,11 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B633:B667 B669:B1048576 C668 B1:B630 C631">
-    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
+  <conditionalFormatting sqref="B668:B1048576 B633:B666 C667 B1:B630 C631">
+    <cfRule type="duplicateValues" dxfId="12" priority="109"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C633:C667 C669:C1048576 C1:C630">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+  <conditionalFormatting sqref="C668:C1048576 C633:C666 C1:C630">
+    <cfRule type="duplicateValues" dxfId="11" priority="115"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="B449" r:id="rId1" xr:uid="{9BCE4324-8A77-884E-80ED-4C3988C2A1D3}"/>
